--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487988_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487988_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.000299999999999</v>
+        <v>7.6242</v>
       </c>
       <c r="E2" t="n">
-        <v>8.122400000000001</v>
+        <v>7.4093</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1221</v>
+        <v>0.2148</v>
       </c>
       <c r="G2" t="n">
         <v>5.6851</v>
@@ -610,13 +610,13 @@
         <v>2.7751</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3422</v>
+        <v>-0.034</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5399</v>
+        <v>-0.1732</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1977</v>
+        <v>0.1393</v>
       </c>
       <c r="V2" t="n">
         <v>0.3873</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1554</v>
+        <v>4.4258</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3788</v>
+        <v>2.4807</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7767</v>
+        <v>1.9451</v>
       </c>
       <c r="G3" t="n">
         <v>4.6618</v>
@@ -688,13 +688,13 @@
         <v>2.3787</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.42</v>
+        <v>-0.1496</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3816</v>
+        <v>-0.2798</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0383</v>
+        <v>0.1301</v>
       </c>
       <c r="V3" t="n">
         <v>-0.4828</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4522</v>
+        <v>4.2808</v>
       </c>
       <c r="E4" t="n">
-        <v>4.9041</v>
+        <v>5.3116</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.4519</v>
+        <v>-1.0307</v>
       </c>
       <c r="G4" t="n">
         <v>4.4373</v>
@@ -766,13 +766,13 @@
         <v>1.9822</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.6573</v>
+        <v>-0.8287</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1232</v>
+        <v>-0.7157</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5342</v>
+        <v>-0.113</v>
       </c>
       <c r="V4" t="n">
         <v>-0.1207</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9785</v>
+        <v>2.8424</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8345</v>
+        <v>1.4457</v>
       </c>
       <c r="F5" t="n">
-        <v>1.144</v>
+        <v>1.3967</v>
       </c>
       <c r="G5" t="n">
         <v>1.1254</v>
@@ -844,13 +844,13 @@
         <v>1.1893</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.4173</v>
+        <v>-0.5534</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1232</v>
+        <v>-0.5119</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2942</v>
+        <v>-0.0415</v>
       </c>
       <c r="V5" t="n">
         <v>2.0722</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K. OULAI</t>
+          <t>J. YELAMOS MAÑAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8094</v>
+        <v>0.6027</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0689</v>
+        <v>0.6027</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8783</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.955</v>
+        <v>0.6027</v>
       </c>
       <c r="H6" t="n">
-        <v>1.906</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9510999999999999</v>
+        <v>0.6027</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3115</v>
+        <v>0.6027</v>
       </c>
       <c r="K6" t="n">
-        <v>2.1463</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1.1652</v>
+        <v>0.6027</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.3565</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2403</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.1162</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.1627</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1805</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.0529</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0769</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.1297</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2163</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1408</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.0755</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. YELAMOS MAÑAS</t>
+          <t>M. DIARRA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6027</v>
+        <v>0.0678</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6027</v>
+        <v>-0.4681</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>0.5359</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6027</v>
+        <v>0.0965</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>-0.2057</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6027</v>
+        <v>0.3022</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6027</v>
+        <v>1.0167</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>-0.3494</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6027</v>
+        <v>1.366</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-0.9201</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.1437</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-1.0638</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1893</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.3876</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0.2973</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-0.2954</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0.0019</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.0704</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.0704</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. DIARRA</t>
+          <t>A. RODRIGUEZ VILLEGAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1921</v>
+        <v>-0.7819</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6719000000000001</v>
+        <v>-1.1159</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4798</v>
+        <v>0.334</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0965</v>
+        <v>0.2717</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2057</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3022</v>
+        <v>0.2717</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0167</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3494</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1.366</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9201</v>
+        <v>0.2717</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1437</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0638</v>
+        <v>0.2717</v>
       </c>
       <c r="P8" t="n">
+        <v>-0.7929</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-0.9911</v>
+      </c>
+      <c r="R8" t="n">
         <v>0.1982</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-1.1893</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.3876</v>
-      </c>
       <c r="S8" t="n">
-        <v>-0.5572</v>
+        <v>-0.2606</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4992</v>
+        <v>-0.1248</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0581</v>
+        <v>-0.1358</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0704</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0704</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. GIMENEZ SALAZAR</t>
+          <t>K. OULAI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6208</v>
+        <v>-0.8159</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8915999999999999</v>
+        <v>-1.3745</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5124</v>
+        <v>0.5586</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2984</v>
+        <v>0.955</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4478</v>
+        <v>1.906</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7463</v>
+        <v>-0.9510999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>1.4662</v>
+        <v>3.3115</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.181</v>
+        <v>2.1463</v>
       </c>
       <c r="L9" t="n">
-        <v>1.6473</v>
+        <v>1.1652</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7647</v>
+        <v>-2.3565</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6289</v>
+        <v>-0.2403</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.3936</v>
+        <v>-2.1162</v>
       </c>
       <c r="P9" t="n">
-        <v>2.3787</v>
+        <v>-1.9822</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.1982</v>
+        <v>-4.1627</v>
       </c>
       <c r="R9" t="n">
-        <v>2.5769</v>
+        <v>2.1805</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7492</v>
+        <v>0.4276</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2975</v>
+        <v>-0.3825</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4517</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>-3.4503</v>
+        <v>-0.2163</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.674</v>
+        <v>-0.1408</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.7763</v>
+        <v>-0.0755</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ VILLEGAS</t>
+          <t>B. GIMENEZ SALAZAR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7819</v>
+        <v>-1.0002</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1159</v>
+        <v>0.4841</v>
       </c>
       <c r="F10" t="n">
-        <v>0.334</v>
+        <v>-1.4843</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2717</v>
+        <v>-0.2984</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.4478</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2717</v>
+        <v>-0.7463</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1.4662</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>-0.181</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.6473</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2717</v>
+        <v>-1.7647</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>0.6289</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2717</v>
+        <v>-2.3936</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.7929</v>
+        <v>2.3787</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9911</v>
+        <v>-0.1982</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1982</v>
+        <v>2.5769</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2606</v>
+        <v>0.3698</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1248</v>
+        <v>-0.11</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1358</v>
+        <v>0.4798</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-3.4503</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.674</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-2.7763</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2157</v>
+        <v>-4.0577</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.427</v>
+        <v>-3.3251</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7887</v>
+        <v>-0.7326</v>
       </c>
       <c r="G11" t="n">
         <v>-0.6923</v>
@@ -1312,13 +1312,13 @@
         <v>1.1893</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8692</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8112</v>
+        <v>-0.7093</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0581</v>
+        <v>-0.0019</v>
       </c>
       <c r="V11" t="n">
         <v>-0.8701</v>
@@ -1348,19 +1348,19 @@
         <v>13.188</v>
       </c>
       <c r="E12" t="n">
-        <v>11.4504</v>
+        <v>11.4505</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7377</v>
+        <v>1.7375</v>
       </c>
       <c r="G12" t="n">
         <v>16.8448</v>
       </c>
       <c r="H12" t="n">
-        <v>8.129899999999999</v>
+        <v>8.129900000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>8.714599999999999</v>
+        <v>8.714600000000001</v>
       </c>
       <c r="J12" t="n">
         <v>27.2206</v>
@@ -1390,13 +1390,13 @@
         <v>15.8578</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.0373</v>
+        <v>-2.0374</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.3027</v>
+        <v>-3.3026</v>
       </c>
       <c r="U12" t="n">
-        <v>1.265</v>
+        <v>1.2651</v>
       </c>
       <c r="V12" t="n">
         <v>-2.6103</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.8122</v>
+        <v>2.5947</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2997</v>
+        <v>2.5035</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5125</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-1.4912</v>
@@ -1468,13 +1468,13 @@
         <v>1.784</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3122</v>
+        <v>1.0948</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0072</v>
+        <v>0.1965</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3195</v>
+        <v>0.8983</v>
       </c>
       <c r="V13" t="n">
         <v>1.2071</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3984</v>
+        <v>2.1043</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2371</v>
+        <v>2.7465</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8387</v>
+        <v>-0.6421</v>
       </c>
       <c r="G14" t="n">
         <v>3.3129</v>
@@ -1546,13 +1546,13 @@
         <v>1.784</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.1831</v>
+        <v>-0.4772</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8112</v>
+        <v>-0.3018</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3719</v>
+        <v>-0.1754</v>
       </c>
       <c r="V14" t="n">
         <v>-0.5331</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0658</v>
+        <v>0.1764</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2315</v>
+        <v>-0.1296</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1656</v>
+        <v>0.306</v>
       </c>
       <c r="G16" t="n">
         <v>-0.0457</v>
@@ -1702,13 +1702,13 @@
         <v>0.1982</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2184</v>
+        <v>0.0239</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.312</v>
+        <v>-0.2101</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0936</v>
+        <v>0.234</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. LEGANOVIC</t>
+          <t>M. FERNANDEZ GIL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1097</v>
+        <v>-0.5508</v>
       </c>
       <c r="E17" t="n">
-        <v>4.4126</v>
+        <v>-0.646</v>
       </c>
       <c r="F17" t="n">
-        <v>-4.5223</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1443</v>
+        <v>-2.6734</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9203</v>
+        <v>-2.3843</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.224</v>
+        <v>-0.289</v>
       </c>
       <c r="J17" t="n">
-        <v>3.5098</v>
+        <v>-0.8837</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1349</v>
+        <v>-1.6471</v>
       </c>
       <c r="L17" t="n">
-        <v>3.3749</v>
+        <v>0.7634</v>
       </c>
       <c r="M17" t="n">
-        <v>-4.6541</v>
+        <v>-1.7896</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0552</v>
+        <v>-0.7372</v>
       </c>
       <c r="O17" t="n">
-        <v>-3.5989</v>
+        <v>-1.0524</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.9911</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9822</v>
+        <v>0.9911</v>
       </c>
       <c r="S17" t="n">
-        <v>1.7086</v>
+        <v>0.5983000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>2.0853</v>
+        <v>-0.2954</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3767</v>
+        <v>0.8937</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.674</v>
+        <v>0.5331</v>
       </c>
       <c r="W17" t="n">
-        <v>0.7997</v>
+        <v>0.5331</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.4737</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. FERNANDEZ GIL</t>
+          <t>A. BUZZO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2491</v>
+        <v>-0.9588</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8498</v>
+        <v>-0.5476</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6006</v>
+        <v>-0.4112</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.6734</v>
+        <v>-0.9172</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.3843</v>
+        <v>1.6521</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.289</v>
+        <v>-2.5693</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.8837</v>
+        <v>2.6036</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.6471</v>
+        <v>2.7851</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7634</v>
+        <v>-0.1814</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.7896</v>
+        <v>-3.5208</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7372</v>
+        <v>-1.1329</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.0524</v>
+        <v>-2.3879</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9911</v>
+        <v>-1.3876</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9911</v>
+        <v>1.5858</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9</v>
+        <v>0.335</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4992</v>
+        <v>-0.1779</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3991</v>
+        <v>0.5129</v>
       </c>
       <c r="V18" t="n">
-        <v>0.5331</v>
+        <v>1.0109</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5331</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.0109</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. BUZZO</t>
+          <t>J. LEGANOVIC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5275</v>
+        <v>-1.3465</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7513</v>
+        <v>2.7827</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7762</v>
+        <v>-4.1292</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.9172</v>
+        <v>-1.1443</v>
       </c>
       <c r="H19" t="n">
-        <v>1.6521</v>
+        <v>-0.9203</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.5693</v>
+        <v>-0.224</v>
       </c>
       <c r="J19" t="n">
-        <v>2.6036</v>
+        <v>3.5098</v>
       </c>
       <c r="K19" t="n">
-        <v>2.7851</v>
+        <v>0.1349</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1814</v>
+        <v>3.3749</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.5208</v>
+        <v>-4.6541</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1329</v>
+        <v>-1.0552</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.3879</v>
+        <v>-3.5989</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.3876</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.9733</v>
+        <v>-1.9822</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5858</v>
+        <v>1.9822</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2338</v>
+        <v>0.4718</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3816</v>
+        <v>0.4554</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1479</v>
+        <v>0.0164</v>
       </c>
       <c r="V19" t="n">
-        <v>1.0109</v>
+        <v>-0.674</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.7997</v>
       </c>
       <c r="X19" t="n">
-        <v>1.0109</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. DIMITROV KOLEV</t>
+          <t>P. LOPEZ GOMEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3529</v>
+        <v>-2.0384</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.9103</v>
+        <v>-0.6005</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5574</v>
+        <v>-1.438</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.0079</v>
+        <v>-3.7626</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.342</v>
+        <v>0.3391</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6659</v>
+        <v>-4.1017</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.8878</v>
+        <v>0.2276</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.0083</v>
+        <v>2.2132</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1205</v>
+        <v>-1.9855</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1201</v>
+        <v>-3.9903</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3337</v>
+        <v>-1.8741</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7864</v>
+        <v>-2.1162</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7929</v>
+        <v>0.5947</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1893</v>
+        <v>1.5858</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8552999999999999</v>
+        <v>-0.3441</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3671</v>
+        <v>-0.6367</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4881</v>
+        <v>0.2926</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.4074</v>
+        <v>1.4737</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.4074</v>
+        <v>0.7997</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. LOPEZ GOMEZ</t>
+          <t>H. VAZQUEZ GARCIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5654</v>
+        <v>-2.4271</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2117</v>
+        <v>0.4021</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3537</v>
+        <v>-2.8292</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.7626</v>
+        <v>-1.0405</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3391</v>
+        <v>-0.4897</v>
       </c>
       <c r="I21" t="n">
-        <v>-4.1017</v>
+        <v>-0.5508</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2276</v>
+        <v>2.3462</v>
       </c>
       <c r="K21" t="n">
-        <v>2.2132</v>
+        <v>-0.0398</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.9855</v>
+        <v>2.386</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.9903</v>
+        <v>-3.3867</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.8741</v>
+        <v>-0.4499</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.1162</v>
+        <v>-2.9369</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5947</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9911</v>
+        <v>-2.9733</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5858</v>
+        <v>1.9822</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8711</v>
+        <v>-0.3955</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.2479</v>
+        <v>-0.1779</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3768</v>
+        <v>-0.2176</v>
       </c>
       <c r="V21" t="n">
-        <v>1.4737</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7997</v>
+        <v>1.2071</v>
       </c>
       <c r="X21" t="n">
-        <v>0.674</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>H. VAZQUEZ GARCIA</t>
+          <t>I. DIMITROV KOLEV</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8836</v>
+        <v>-2.6585</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1984</v>
+        <v>-3.2159</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.0819</v>
+        <v>0.5574</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.0405</v>
+        <v>-2.0079</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4897</v>
+        <v>-1.342</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5508</v>
+        <v>-0.6659</v>
       </c>
       <c r="J22" t="n">
-        <v>2.3462</v>
+        <v>-0.8878</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.0398</v>
+        <v>-1.0083</v>
       </c>
       <c r="L22" t="n">
-        <v>2.386</v>
+        <v>0.1205</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.3867</v>
+        <v>-1.1201</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4499</v>
+        <v>-0.3337</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.9369</v>
+        <v>-0.7864</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9911</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9733</v>
+        <v>-1.9822</v>
       </c>
       <c r="R22" t="n">
-        <v>1.9822</v>
+        <v>1.1893</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8519</v>
+        <v>0.5497</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3816</v>
+        <v>0.0615</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4703</v>
+        <v>0.4881</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.4074</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2071</v>
+        <v>-0.4074</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.2498</v>
+        <v>-8.688700000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.5363</v>
+        <v>-5.6381</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.7136</v>
+        <v>-3.0505</v>
       </c>
       <c r="G23" t="n">
         <v>-7.6801</v>
@@ -2248,13 +2248,13 @@
         <v>1.784</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6196</v>
+        <v>0.1808</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0769</v>
+        <v>-0.1787</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6965</v>
+        <v>0.3596</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,10 +2281,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-13.1879</v>
+        <v>-13.1881</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.7378</v>
+        <v>-1.7376</v>
       </c>
       <c r="F24" t="n">
         <v>-11.4503</v>
@@ -2302,13 +2302,13 @@
         <v>10.3757</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.1766000000000001</v>
+        <v>-0.1765999999999996</v>
       </c>
       <c r="L24" t="n">
         <v>10.5526</v>
       </c>
       <c r="M24" t="n">
-        <v>-27.22040000000001</v>
+        <v>-27.2204</v>
       </c>
       <c r="N24" t="n">
         <v>-7.9533</v>
@@ -2317,7 +2317,7 @@
         <v>-19.2672</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.9911</v>
+        <v>-0.9910999999999999</v>
       </c>
       <c r="Q24" t="n">
         <v>-15.8576</v>
@@ -2326,10 +2326,10 @@
         <v>14.8666</v>
       </c>
       <c r="S24" t="n">
-        <v>2.0374</v>
+        <v>2.0375</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.2652</v>
+        <v>-1.2651</v>
       </c>
       <c r="U24" t="n">
         <v>3.3026</v>
@@ -2338,7 +2338,7 @@
         <v>2.6103</v>
       </c>
       <c r="W24" t="n">
-        <v>5.0094</v>
+        <v>5.009399999999999</v>
       </c>
       <c r="X24" t="n">
         <v>-2.3991</v>
